--- a/schedules/users.xlsx
+++ b/schedules/users.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -488,26 +488,26 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2258383153</v>
+        <v>1318145972</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2403656</t>
+          <t>2502964</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>赵芮</t>
+          <t>李如军</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2024226501</t>
+          <t>2025242302</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24大数据1班</t>
+          <t>25汽车智能2班</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -515,50 +515,50 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>195e0239f8e146c488e1538b54249e4e</t>
+          <t>d4f3717fbb6648c3b1bbe59c92f1dd4d</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>computerf89f90b991f8441bbc3f602e01eaf8d7</t>
+          <t>computerce62c51b15364ad498cb783a50785d40</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1780556124</v>
+        <v>1780666129</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-06-04T13:55:24</t>
+          <t>2026-06-05T20:28:49</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-06-04T13:55:24</t>
+          <t>2026-06-05T20:28:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2972033204</v>
+        <v>1639392228</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2404281</t>
+          <t>2403941</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>吴建城</t>
+          <t>戴小林</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2024227401</t>
+          <t>2024226503</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24信息安全1班</t>
+          <t>24大数据3班（学徒制）</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -566,50 +566,50 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>aef3a37d08bf452792d426dd213a0a6a</t>
+          <t>24d96222c9af4f4d9055b8be8043edb5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>computer7de3856e6b1c444d8218f18f29447d0e</t>
+          <t>computerae0dae3e98b7479f8ad203a0c2b1ebaf</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1780560362</v>
+        <v>1780658185</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-06-04T15:06:02</t>
+          <t>2026-06-05T18:16:25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-06-04T15:06:03</t>
+          <t>2026-06-05T18:16:25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3200418862</v>
+        <v>2258383153</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2403740</t>
+          <t>2403656</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>沈昱作</t>
+          <t>赵芮</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2024226503</t>
+          <t>2024226501</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24大数据3班（学徒制）</t>
+          <t>24大数据1班</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -617,50 +617,50 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>01230e997f0d4a44a12bc024f4d27397</t>
+          <t>195e0239f8e146c488e1538b54249e4e</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>002f7a906718b1146628364738edfe19387</t>
+          <t>computerf89f90b991f8441bbc3f602e01eaf8d7</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1780556124</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-06-05T16:01:07</t>
+          <t>2026-06-04T13:55:24</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-06-01T15:28:27</t>
+          <t>2026-06-04T13:55:24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3371492477</v>
+        <v>2972033204</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2405134</t>
+          <t>2404281</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>舒文</t>
+          <t>吴建城</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2024240501</t>
+          <t>2024227401</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24汽车制造与试验班</t>
+          <t>24信息安全1班</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -668,23 +668,125 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ab398252924246a8b6e1731498defbd5</t>
+          <t>aef3a37d08bf452792d426dd213a0a6a</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0028c4ff3bf1d7e4c5a90b134bf572de7b0</t>
+          <t>computer7de3856e6b1c444d8218f18f29447d0e</t>
         </is>
       </c>
       <c r="I5" t="n">
+        <v>1780560362</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-04T15:06:02</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-06-04T15:06:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>3200418862</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2403740</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>沈昱作</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2024226503</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>24大数据3班（学徒制）</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-04T18:21:19</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>01211f9509ba41348681570f7b961e7c</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>002c6311cd8581848108fec6d4118fc11f6</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-07T16:12:11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-06-01T15:28:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>3602653998</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2405134</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>舒文</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2024240501</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>24汽车制造与试验班</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>d02e21a3936640d9b6209161d05c30b6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>00255036bea1f644b1e9b75e73774fe20e6</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-07T17:06:33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>2026-06-01T17:10:59</t>
         </is>
